--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB29553-A0A8-4F59-87A7-8977B3F7E64D}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142F6FD5-F110-4020-A08E-4091C9CBFDFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="73">
   <si>
     <t>S/N</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>Charging consent of quality lab from CEI</t>
+  </si>
+  <si>
+    <t>28/08/2027</t>
+  </si>
+  <si>
+    <t>Charging consent of GMBS</t>
+  </si>
+  <si>
+    <t>Done 29/08/2026</t>
   </si>
 </sst>
 </file>
@@ -688,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1375,26 +1384,74 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="14">
+      <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G28" s="17"/>
-      <c r="H28" s="13"/>
+      <c r="G28" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="22"/>
+    </row>
+    <row r="29" spans="1:8" ht="11.25">
+      <c r="A29" s="14">
+        <v>28</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="14"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="13"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="14"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1404,15 +1461,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1617,6 +1665,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1626,11 +1683,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142F6FD5-F110-4020-A08E-4091C9CBFDFD}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BC61BF-1AAB-4F1E-877F-D0DE9B44A22E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,7 +277,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +287,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -393,6 +399,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1228,7 +1236,7 @@
       <c r="B21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="23" t="s">
         <v>60</v>
       </c>
       <c r="D21" s="17" t="s">
@@ -1254,7 +1262,7 @@
       <c r="B22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="23" t="s">
         <v>63</v>
       </c>
       <c r="D22" s="17" t="s">
@@ -1390,7 +1398,7 @@
       <c r="B28" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="24" t="s">
         <v>69</v>
       </c>
       <c r="D28" s="20" t="s">
@@ -1414,7 +1422,7 @@
       <c r="B29" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="23" t="s">
         <v>71</v>
       </c>
       <c r="D29" s="17" t="s">
@@ -1461,6 +1469,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1665,15 +1682,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1683,11 +1691,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BC61BF-1AAB-4F1E-877F-D0DE9B44A22E}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DF488C-7637-4B0F-A079-F142BC0129BA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="72">
   <si>
     <t>S/N</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>1st time</t>
-  </si>
-  <si>
-    <t>Rail alignment of EOT cranes</t>
   </si>
   <si>
     <t>Charging consent Hydrogen plant from CEI</t>
@@ -337,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -391,9 +388,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1210,37 +1204,43 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="11.25">
-      <c r="A20" s="19">
-        <v>19</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="A20" s="14">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="19" t="s">
+      <c r="D20" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="22"/>
+      <c r="G20" s="15">
+        <v>46571</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="11.25">
       <c r="A21" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>61</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>29</v>
@@ -1252,21 +1252,21 @@
         <v>46571</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="11.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="14" t="s">
         <v>63</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>29</v>
@@ -1274,16 +1274,12 @@
       <c r="F22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="15">
-        <v>46571</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>62</v>
-      </c>
+      <c r="G22" s="17"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>27</v>
@@ -1292,7 +1288,7 @@
         <v>64</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>29</v>
@@ -1305,7 +1301,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>27</v>
@@ -1314,7 +1310,7 @@
         <v>65</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>29</v>
@@ -1327,7 +1323,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>27</v>
@@ -1336,7 +1332,7 @@
         <v>66</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>29</v>
@@ -1349,7 +1345,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>27</v>
@@ -1358,7 +1354,7 @@
         <v>67</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>29</v>
@@ -1370,76 +1366,64 @@
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="14">
-        <v>26</v>
-      </c>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="19">
         <v>27</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="B27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="14" t="s">
+      <c r="D27" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="19">
+      <c r="G27" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" ht="11.25">
+      <c r="A28" s="14">
+        <v>28</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="22"/>
-    </row>
-    <row r="29" spans="1:8" ht="11.25">
-      <c r="A29" s="14">
-        <v>28</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="23" t="s">
+      <c r="H28" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>72</v>
-      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="14"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="13"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="14"/>
@@ -1451,16 +1435,7 @@
       <c r="G30" s="17"/>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="14"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="13"/>
-    </row>
+    <row r="31" spans="1:8" ht="11.25"/>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DF488C-7637-4B0F-A079-F142BC0129BA}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8B4F68-03A5-4A06-8693-D1BE75F0E13B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>S/N</t>
   </si>
@@ -252,6 +252,15 @@
   </si>
   <si>
     <t>Done 29/08/2026</t>
+  </si>
+  <si>
+    <t>AERB certicate renewal</t>
+  </si>
+  <si>
+    <t>30/7/2028</t>
+  </si>
+  <si>
+    <t>Renewed on 30/07/25</t>
   </si>
 </sst>
 </file>
@@ -1415,15 +1424,31 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="14"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="13"/>
+    <row r="29" spans="1:8" ht="11.25">
+      <c r="A29" s="14">
+        <v>29</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="14"/>
@@ -1444,15 +1469,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1657,6 +1673,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1666,11 +1691,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30509"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8B4F68-03A5-4A06-8693-D1BE75F0E13B}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A3DF67D-E583-4A6A-A0C8-6EE644F9C0F7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
     <t>Done 29/08/2026</t>
   </si>
   <si>
-    <t>AERB certicate renewal</t>
+    <t>AERB certificate renewal</t>
   </si>
   <si>
     <t>30/7/2028</t>
@@ -1469,6 +1469,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1673,15 +1682,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1691,11 +1691,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A3DF67D-E583-4A6A-A0C8-6EE644F9C0F7}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFB4617-E9EB-4F0D-873E-E426F4E75FD5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
     <t>Done 29/08/2026</t>
   </si>
   <si>
-    <t>AERB certificate renewal</t>
+    <t>AERB institute certificate renewal-JSL</t>
   </si>
   <si>
     <t>30/7/2028</t>
@@ -1469,15 +1469,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1682,6 +1673,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1691,11 +1691,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAFB4617-E9EB-4F0D-873E-E426F4E75FD5}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA34ECEE-1C4B-43A8-BC6C-DF59786D76D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -722,7 +722,7 @@
     <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="11.25">
+    <row r="1" spans="1:8" ht="16.5" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA34ECEE-1C4B-43A8-BC6C-DF59786D76D2}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCB07CB-3836-4AA1-844E-F398995135C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,6 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
@@ -748,7 +749,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="11.25">
+    <row r="2" spans="1:8" ht="11.25" hidden="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -774,7 +775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="11.25">
+    <row r="3" spans="1:8" ht="11.25" hidden="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -800,7 +801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="11.25">
+    <row r="4" spans="1:8" ht="11.25" hidden="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -826,7 +827,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" customHeight="1">
+    <row r="5" spans="1:8" ht="13.5" hidden="1" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -852,7 +853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="46.5">
+    <row r="6" spans="1:8" ht="46.5" hidden="1">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -878,7 +879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="23.25">
+    <row r="7" spans="1:8" ht="23.25" hidden="1">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -904,7 +905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="11.25">
+    <row r="8" spans="1:8" ht="11.25" hidden="1">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="23.25">
+    <row r="16" spans="1:8" ht="23.25" hidden="1">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="11.25">
+    <row r="17" spans="1:8" ht="11.25" hidden="1">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -1162,7 +1163,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="11.25">
+    <row r="18" spans="1:8" ht="11.25" hidden="1">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -1186,7 +1187,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="11.25">
+    <row r="19" spans="1:8" ht="11.25" hidden="1">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="11.25">
+    <row r="20" spans="1:8" ht="11.25" hidden="1">
       <c r="A20" s="14">
         <v>20</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="11.25">
+    <row r="21" spans="1:8" ht="11.25" hidden="1">
       <c r="A21" s="14">
         <v>21</v>
       </c>
@@ -1264,7 +1265,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" s="14">
         <v>22</v>
       </c>
@@ -1286,7 +1287,7 @@
       <c r="G22" s="17"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" hidden="1">
       <c r="A23" s="14">
         <v>23</v>
       </c>
@@ -1308,7 +1309,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" hidden="1">
       <c r="A24" s="14">
         <v>24</v>
       </c>
@@ -1330,7 +1331,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" s="14">
         <v>25</v>
       </c>
@@ -1352,7 +1353,7 @@
       <c r="G25" s="17"/>
       <c r="H25" s="13"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" hidden="1">
       <c r="A26" s="14">
         <v>26</v>
       </c>
@@ -1374,7 +1375,7 @@
       <c r="G26" s="17"/>
       <c r="H26" s="13"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" hidden="1">
       <c r="A27" s="19">
         <v>27</v>
       </c>
@@ -1398,7 +1399,7 @@
       </c>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="11.25">
+    <row r="28" spans="1:8" ht="11.25" hidden="1">
       <c r="A28" s="14">
         <v>28</v>
       </c>
@@ -1424,7 +1425,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="11.25">
+    <row r="29" spans="1:8" ht="11.25" hidden="1">
       <c r="A29" s="14">
         <v>29</v>
       </c>
@@ -1462,13 +1463,36 @@
     </row>
     <row r="31" spans="1:8" ht="11.25"/>
   </sheetData>
-  <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Saroj Kumar Panda"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1673,25 +1697,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1699,5 +1706,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCB07CB-3836-4AA1-844E-F398995135C8}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B7740E-7B6F-4E17-804F-981FE9B2C603}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,7 +708,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="10.15"/>
   <cols>
@@ -749,7 +748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="11.25" hidden="1">
+    <row r="2" spans="1:8" ht="11.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -775,7 +774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="11.25" hidden="1">
+    <row r="3" spans="1:8" ht="11.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -801,7 +800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="11.25" hidden="1">
+    <row r="4" spans="1:8" ht="11.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -827,7 +826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="13.5" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -853,7 +852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="46.5" hidden="1">
+    <row r="6" spans="1:8" ht="46.5">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -879,7 +878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="23.25" hidden="1">
+    <row r="7" spans="1:8" ht="23.25">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -905,7 +904,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="11.25" hidden="1">
+    <row r="8" spans="1:8" ht="11.25">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -1113,7 +1112,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="23.25" hidden="1">
+    <row r="16" spans="1:8" ht="23.25">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -1139,7 +1138,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="11.25" hidden="1">
+    <row r="17" spans="1:8" ht="11.25">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -1163,7 +1162,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="11.25" hidden="1">
+    <row r="18" spans="1:8" ht="11.25">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -1187,7 +1186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="11.25" hidden="1">
+    <row r="19" spans="1:8" ht="11.25">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -1213,7 +1212,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="11.25" hidden="1">
+    <row r="20" spans="1:8" ht="11.25">
       <c r="A20" s="14">
         <v>20</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="11.25" hidden="1">
+    <row r="21" spans="1:8" ht="11.25">
       <c r="A21" s="14">
         <v>21</v>
       </c>
@@ -1265,7 +1264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1">
+    <row r="22" spans="1:8">
       <c r="A22" s="14">
         <v>22</v>
       </c>
@@ -1287,7 +1286,7 @@
       <c r="G22" s="17"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8" hidden="1">
+    <row r="23" spans="1:8">
       <c r="A23" s="14">
         <v>23</v>
       </c>
@@ -1309,7 +1308,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="13"/>
     </row>
-    <row r="24" spans="1:8" hidden="1">
+    <row r="24" spans="1:8">
       <c r="A24" s="14">
         <v>24</v>
       </c>
@@ -1331,7 +1330,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" hidden="1">
+    <row r="25" spans="1:8">
       <c r="A25" s="14">
         <v>25</v>
       </c>
@@ -1353,7 +1352,7 @@
       <c r="G25" s="17"/>
       <c r="H25" s="13"/>
     </row>
-    <row r="26" spans="1:8" hidden="1">
+    <row r="26" spans="1:8">
       <c r="A26" s="14">
         <v>26</v>
       </c>
@@ -1375,7 +1374,7 @@
       <c r="G26" s="17"/>
       <c r="H26" s="13"/>
     </row>
-    <row r="27" spans="1:8" hidden="1">
+    <row r="27" spans="1:8">
       <c r="A27" s="19">
         <v>27</v>
       </c>
@@ -1399,7 +1398,7 @@
       </c>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="11.25" hidden="1">
+    <row r="28" spans="1:8" ht="11.25">
       <c r="A28" s="14">
         <v>28</v>
       </c>
@@ -1425,7 +1424,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="11.25" hidden="1">
+    <row r="29" spans="1:8" ht="11.25">
       <c r="A29" s="14">
         <v>29</v>
       </c>
@@ -1463,13 +1462,7 @@
     </row>
     <row r="31" spans="1:8" ht="11.25"/>
   </sheetData>
-  <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Saroj Kumar Panda"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B7740E-7B6F-4E17-804F-981FE9B2C603}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C686F51-1C84-4175-A4B7-ED87050B32D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="80">
   <si>
     <t>S/N</t>
   </si>
@@ -261,6 +261,21 @@
   </si>
   <si>
     <t>Renewed on 30/07/25</t>
+  </si>
+  <si>
+    <t>CTO from pollution control board of Mill-3 and 4</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Satyanarayan</t>
+  </si>
+  <si>
+    <t>CTO from pollution control board of  BA#5 and 6</t>
+  </si>
+  <si>
+    <t>Done on 17.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1453,14 +1468,38 @@
     <row r="30" spans="1:8">
       <c r="A30" s="14"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="C30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="G30" s="17"/>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" spans="1:8" ht="11.25"/>
+    <row r="31" spans="1:8" ht="11.25">
+      <c r="C31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.27" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1469,23 +1508,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1690,8 +1712,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1699,5 +1738,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C686F51-1C84-4175-A4B7-ED87050B32D7}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC22CB8A-E91C-46C4-BB18-85D6C60DBEE4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="81">
   <si>
     <t>S/N</t>
   </si>
@@ -272,10 +272,13 @@
     <t>Satyanarayan</t>
   </si>
   <si>
+    <t>31.03.2027</t>
+  </si>
+  <si>
+    <t>Done on 17.09.2026</t>
+  </si>
+  <si>
     <t>CTO from pollution control board of  BA#5 and 6</t>
-  </si>
-  <si>
-    <t>Done on 17.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1465,9 +1468,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="14"/>
-      <c r="B30" s="17"/>
+    <row r="30" spans="1:8" ht="11.25">
+      <c r="A30" s="14">
+        <v>30</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="C30" s="14" t="s">
         <v>75</v>
       </c>
@@ -1480,12 +1487,22 @@
       <c r="F30" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="13"/>
+      <c r="G30" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="11.25">
+      <c r="A31" s="1">
+        <v>31</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>76</v>
@@ -1495,6 +1512,9 @@
       </c>
       <c r="F31" s="14" t="s">
         <v>25</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>79</v>
@@ -1508,6 +1528,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1712,31 +1749,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>
--- a/Data/compliance_master.xlsx
+++ b/Data/compliance_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC22CB8A-E91C-46C4-BB18-85D6C60DBEE4}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{33421BAC-B902-40FB-9F3E-EE7CD05BE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8808E267-F340-41CC-BE49-F682444EF732}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1443,28 +1443,28 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="11.25">
-      <c r="A29" s="14">
+      <c r="A29" s="19">
         <v>29</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="21" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1490,21 +1490,21 @@
       <c r="G30" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="11.25">
-      <c r="A31" s="1">
+      <c r="A31" s="14">
         <v>31</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E31" s="14" t="s">
@@ -1516,7 +1516,7 @@
       <c r="G31" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="13" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1528,23 +1528,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFAA606C4D50A42858F88A84D40BC63" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa344f6f3009089f0fd14ea778a7e517">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xmlns:ns4="af781878-b04d-4d18-a5ad-eebfe8fcc07f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="06e62eee0f65df8579ea929df8d260f1" ns3:_="" ns4:_="">
     <xsd:import namespace="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c"/>
@@ -1749,14 +1732,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ecea5bc9-cb94-4a3c-a7e5-cc5d6b4eab6c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366BFB7-7237-42BC-86C1-F0EB7BAE611E}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE30F86D-1BB0-400B-9278-71936245B8BE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEA998B2-1415-42FB-B209-9A96B5C2DC40}"/>
 </file>